--- a/results/breakdown/2020/hydrogen peroxide production, AO, green hydrogen.xlsx
+++ b/results/breakdown/2020/hydrogen peroxide production, AO, green hydrogen.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="13">
   <si>
     <t>target</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t>'market for wastewater, average' (cubic meter, RoW, None)</t>
+  </si>
+  <si>
+    <t>'market for palladium' (kilogram, GLO, None)</t>
   </si>
   <si>
     <t>'market group for electricity, high voltage' (kilowatt hour, GLO, None)</t>
@@ -407,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -426,7 +429,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
@@ -435,7 +438,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>0.4922014081988072</v>
+        <v>0.4922305672476476</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -452,7 +455,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>0.1405427029304539</v>
+        <v>0.1405427029304538</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -486,7 +489,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>0.004473779517525409</v>
+        <v>0.004473779517525415</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -503,7 +506,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>0.00024357926728292</v>
+        <v>0.0002435792672829192</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -520,7 +523,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>0.06008484844983375</v>
+        <v>2.91590489513779E-05</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -537,7 +540,7 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>0.001051107755855215</v>
+        <v>0.06008484844983379</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -554,9 +557,26 @@
         <v>11</v>
       </c>
       <c r="D9">
+        <v>0.001051107755855214</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10">
         <v>0.1373612714488579</v>
       </c>
-      <c r="E9">
+      <c r="E10">
         <v>1</v>
       </c>
     </row>

--- a/results/breakdown/2020/hydrogen peroxide production, AO, green hydrogen.xlsx
+++ b/results/breakdown/2020/hydrogen peroxide production, AO, green hydrogen.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="12">
   <si>
     <t>target</t>
   </si>
@@ -41,9 +41,6 @@
   </si>
   <si>
     <t>'market for wastewater, average' (cubic meter, RoW, None)</t>
-  </si>
-  <si>
-    <t>'market for palladium' (kilogram, GLO, None)</t>
   </si>
   <si>
     <t>'market group for electricity, high voltage' (kilowatt hour, GLO, None)</t>
@@ -410,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -429,7 +426,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
@@ -438,7 +435,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>0.4922305672476476</v>
+        <v>0.4922014082036287</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -455,7 +452,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>0.1405427029304538</v>
+        <v>0.1405427029349793</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -472,7 +469,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>0.06711642649726114</v>
+        <v>0.06711642649726195</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -489,7 +486,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>0.004473779517525415</v>
+        <v>0.004473779517560401</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -506,7 +503,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>0.0002435792672829192</v>
+        <v>0.0002435792672912285</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -523,7 +520,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>2.91590489513779E-05</v>
+        <v>0.06008484844988556</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -540,7 +537,7 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>0.06008484844983379</v>
+        <v>0.001051107755856121</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -557,26 +554,9 @@
         <v>11</v>
       </c>
       <c r="D9">
-        <v>0.001051107755855214</v>
+        <v>0.1373612714490574</v>
       </c>
       <c r="E9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="1">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10">
-        <v>0.1373612714488579</v>
-      </c>
-      <c r="E10">
         <v>1</v>
       </c>
     </row>

--- a/results/breakdown/2020/hydrogen peroxide production, AO, green hydrogen.xlsx
+++ b/results/breakdown/2020/hydrogen peroxide production, AO, green hydrogen.xlsx
@@ -435,7 +435,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>0.4922014082036287</v>
+        <v>0.4922014082036286</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -452,7 +452,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>0.1405427029349793</v>
+        <v>0.140542702934979</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -486,7 +486,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>0.004473779517560401</v>
+        <v>0.0044737795175604</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -503,7 +503,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>0.0002435792672912285</v>
+        <v>0.0002435792672912273</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -520,7 +520,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>0.06008484844988556</v>
+        <v>0.0600848484498856</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -537,7 +537,7 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>0.001051107755856121</v>
+        <v>0.00105110775585612</v>
       </c>
       <c r="E8">
         <v>1</v>
